--- a/artfynd/A 20728-2023 artfynd.xlsx
+++ b/artfynd/A 20728-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 20728-2023 artfynd.xlsx
+++ b/artfynd/A 20728-2023 artfynd.xlsx
@@ -2037,7 +2037,7 @@
         <v>109507385</v>
       </c>
       <c r="B13" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>

--- a/artfynd/A 20728-2023 artfynd.xlsx
+++ b/artfynd/A 20728-2023 artfynd.xlsx
@@ -2887,7 +2887,7 @@
         <v>0</v>
       </c>
       <c r="AE19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">

--- a/artfynd/A 20728-2023 artfynd.xlsx
+++ b/artfynd/A 20728-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AY20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>109217942</v>
+        <v>109246781</v>
       </c>
       <c r="B2" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,43 +686,48 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Ställbergstjärnmyran, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>501223.3183840729</v>
+        <v>501173</v>
       </c>
       <c r="R2" t="n">
-        <v>6712445.996589876</v>
+        <v>6712542</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -756,7 +756,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -766,15 +766,16 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -793,49 +794,35 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>109246636</v>
+        <v>109246710</v>
       </c>
       <c r="B3" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -843,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>501203.0835188901</v>
+        <v>501173</v>
       </c>
       <c r="R3" t="n">
-        <v>6712542.4102853</v>
+        <v>6712542</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -878,7 +865,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -888,7 +875,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -915,54 +902,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>109246710</v>
+        <v>109507397</v>
       </c>
       <c r="B4" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ställbergstjärnmyran, Dlr</t>
+          <t>Skogstjärn avverkning, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>501173.0266104384</v>
+        <v>501246</v>
       </c>
       <c r="R4" t="n">
-        <v>6712542.400391143</v>
+        <v>6712490</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -986,22 +967,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-05-16</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>16:46</t>
+          <t>2023-05-20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-05-16</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>16:46</t>
+          <t>2023-05-20</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1028,63 +999,54 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>109246655</v>
+        <v>109217942</v>
       </c>
       <c r="B5" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Ställbergstjärnmyran, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>501218.3686373105</v>
+        <v>501223</v>
       </c>
       <c r="R5" t="n">
-        <v>6712511.915329128</v>
+        <v>6712446</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1113,7 +1075,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:53</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1123,7 +1085,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:53</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1150,63 +1112,56 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>109246598</v>
+        <v>109507386</v>
       </c>
       <c r="B6" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Ställbergstjärnmyran, Dlr</t>
+          <t>Skogstjärn avverkning, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>501173.0266104384</v>
+        <v>501216</v>
       </c>
       <c r="R6" t="n">
-        <v>6712542.400391143</v>
+        <v>6712494</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1230,22 +1185,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-05-16</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>16:49</t>
+          <t>2023-05-20</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-05-16</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>16:49</t>
+          <t>2023-05-20</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>färska hack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1272,51 +1222,42 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>109507396</v>
+        <v>109507385</v>
       </c>
       <c r="B7" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1324,10 +1265,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>501188.7894699339</v>
+        <v>501234</v>
       </c>
       <c r="R7" t="n">
-        <v>6712556.671628729</v>
+        <v>6712523</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1357,24 +1298,14 @@
           <t>2023-05-20</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2023-05-20</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>10 st</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1383,7 +1314,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1402,53 +1332,58 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>109507397</v>
+        <v>109246572</v>
       </c>
       <c r="B8" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Skogstjärn avverkning, Dlr</t>
+          <t>Ställbergstjärnmyran, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>501245.9695702925</v>
+        <v>501204</v>
       </c>
       <c r="R8" t="n">
-        <v>6712490.279375424</v>
+        <v>6712542</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1472,22 +1407,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-05-20</t>
+          <t>2023-05-16</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-05-20</t>
+          <t>2023-05-16</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1514,15 +1449,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>109507394</v>
+        <v>109246598</v>
       </c>
       <c r="B9" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1549,7 +1479,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1558,21 +1488,19 @@
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Skogstjärn avverkning, Dlr</t>
+          <t>Ställbergstjärnmyran, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>501217.8641110051</v>
+        <v>501173</v>
       </c>
       <c r="R9" t="n">
-        <v>6712546.842652758</v>
+        <v>6712542</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1596,27 +1524,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-05-20</t>
+          <t>2023-05-16</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-05-20</t>
+          <t>2023-05-16</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>20 st</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1625,7 +1548,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1644,15 +1566,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>109507392</v>
+        <v>109246655</v>
       </c>
       <c r="B10" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1679,7 +1596,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1688,21 +1605,19 @@
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Skogstjärn avverkning, Dlr</t>
+          <t>Ställbergstjärnmyran, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>501231.1659584236</v>
+        <v>501219</v>
       </c>
       <c r="R10" t="n">
-        <v>6712552.75037099</v>
+        <v>6712511</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1726,27 +1641,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-05-20</t>
+          <t>2023-05-16</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:53</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-05-20</t>
+          <t>2023-05-16</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>5 st</t>
+          <t>16:53</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1755,7 +1665,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1774,15 +1683,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>109507390</v>
+        <v>109507387</v>
       </c>
       <c r="B11" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1826,10 +1730,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>501188.8158819623</v>
+        <v>501259</v>
       </c>
       <c r="R11" t="n">
-        <v>6712476.485699432</v>
+        <v>6712531</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1859,19 +1763,9 @@
           <t>2023-05-20</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2023-05-20</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -1904,15 +1798,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>109507391</v>
+        <v>109507388</v>
       </c>
       <c r="B12" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1939,7 +1828,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1956,10 +1845,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>501251.3796833802</v>
+        <v>501161</v>
       </c>
       <c r="R12" t="n">
-        <v>6712519.305699948</v>
+        <v>6712382</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1989,24 +1878,9 @@
           <t>2023-05-20</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2023-05-20</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>100 st</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2034,47 +1908,46 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>109507385</v>
+        <v>109507389</v>
       </c>
       <c r="B13" t="n">
-        <v>57481</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2082,10 +1955,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>501234</v>
+        <v>501165</v>
       </c>
       <c r="R13" t="n">
-        <v>6712523</v>
+        <v>6712394</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -2122,7 +1995,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>10 st</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2131,6 +2004,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2149,15 +2023,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>109507395</v>
+        <v>109507390</v>
       </c>
       <c r="B14" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2201,10 +2070,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>501205.5527867862</v>
+        <v>501189</v>
       </c>
       <c r="R14" t="n">
-        <v>6712525.685288721</v>
+        <v>6712476</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2234,19 +2103,14 @@
           <t>2023-05-20</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2023-05-20</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>10 st</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2274,47 +2138,46 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>109507386</v>
+        <v>109507391</v>
       </c>
       <c r="B15" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2322,10 +2185,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>501215.9110675328</v>
+        <v>501252</v>
       </c>
       <c r="R15" t="n">
-        <v>6712493.71271506</v>
+        <v>6712519</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2355,24 +2218,14 @@
           <t>2023-05-20</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2023-05-20</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>färska hack</t>
+          <t>100 st</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2381,6 +2234,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2399,15 +2253,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>109507393</v>
+        <v>109507392</v>
       </c>
       <c r="B16" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2434,7 +2283,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2451,10 +2300,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>501219.834388331</v>
+        <v>501231</v>
       </c>
       <c r="R16" t="n">
-        <v>6712548.811054256</v>
+        <v>6712553</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2484,24 +2333,14 @@
           <t>2023-05-20</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2023-05-20</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>20 st</t>
+          <t>5 st</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2529,15 +2368,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>109507388</v>
+        <v>109507393</v>
       </c>
       <c r="B17" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2564,7 +2398,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2581,10 +2415,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>501161.2525400028</v>
+        <v>501220</v>
       </c>
       <c r="R17" t="n">
-        <v>6712382.022300528</v>
+        <v>6712549</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2614,19 +2448,14 @@
           <t>2023-05-20</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2023-05-20</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>20 st</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2654,15 +2483,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>109507387</v>
+        <v>109507394</v>
       </c>
       <c r="B18" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2689,7 +2513,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2706,10 +2530,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>501259.2593937377</v>
+        <v>501218</v>
       </c>
       <c r="R18" t="n">
-        <v>6712531.114931141</v>
+        <v>6712547</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2739,24 +2563,14 @@
           <t>2023-05-20</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2023-05-20</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>10 st</t>
+          <t>20 st</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2784,64 +2598,60 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>109246781</v>
+        <v>109507395</v>
       </c>
       <c r="B19" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Ställbergstjärnmyran, Dlr</t>
+          <t>Skogstjärn avverkning, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>501173.0266104384</v>
+        <v>501205</v>
       </c>
       <c r="R19" t="n">
-        <v>6712542.400391143</v>
+        <v>6712525</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2865,29 +2675,19 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2023-05-16</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>16:46</t>
+          <t>2023-05-20</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2023-05-16</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>16:46</t>
+          <t>2023-05-20</t>
         </is>
       </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
@@ -2905,6 +2705,121 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>109507396</v>
+      </c>
+      <c r="B20" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Skogstjärn avverkning, Dlr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>501189</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6712556</v>
+      </c>
+      <c r="S20" t="n">
+        <v>15</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2023-05-20</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2023-05-20</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>10 st</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Erik Garmo</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Erik Garmo</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 20728-2023 artfynd.xlsx
+++ b/artfynd/A 20728-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AZ20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -791,6 +796,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109246781</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -899,6 +909,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109246710</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -996,6 +1011,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109507397</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1109,6 +1129,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109217942</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1219,6 +1244,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109507386</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1329,6 +1359,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109507385</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1446,6 +1481,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109246572</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1563,6 +1603,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109246598</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1680,6 +1725,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109246655</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1795,6 +1845,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109507387</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1905,6 +1960,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109507388</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2020,6 +2080,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109507389</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2135,6 +2200,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109507390</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2250,6 +2320,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109507391</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2365,6 +2440,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109507392</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2480,6 +2560,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109507393</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2595,6 +2680,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109507394</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2705,6 +2795,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109507395</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2820,8 +2915,34 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109507396</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>